--- a/Server/NewServer/bin/commonconfig/setting/guild_achi_cdtn.xlsx
+++ b/Server/NewServer/bin/commonconfig/setting/guild_achi_cdtn.xlsx
@@ -104,7 +104,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>取值范围</t>
+          <t>Allowed range</t>
         </r>
         <r>
           <rPr>
@@ -158,7 +158,7 @@
             <family val="3"/>
             <charset val="134"/>
           </rPr>
-          <t>取值范围</t>
+          <t>Allowed range</t>
         </r>
         <r>
           <rPr>
